--- a/artfynd/A 4776-2025 artfynd.xlsx
+++ b/artfynd/A 4776-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2156,6 +2156,121 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122785011</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106009</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Varberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>327473</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6351451</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ask (EN) 4 stycken och föryngring. Döda skott sy</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4776-2025 artfynd.xlsx
+++ b/artfynd/A 4776-2025 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>122785011</v>
       </c>
       <c r="B14" t="n">
-        <v>106009</v>
+        <v>106017</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 4776-2025 artfynd.xlsx
+++ b/artfynd/A 4776-2025 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>122785011</v>
       </c>
       <c r="B14" t="n">
-        <v>106017</v>
+        <v>106019</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 4776-2025 artfynd.xlsx
+++ b/artfynd/A 4776-2025 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>122785011</v>
       </c>
       <c r="B14" t="n">
-        <v>106019</v>
+        <v>106027</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 4776-2025 artfynd.xlsx
+++ b/artfynd/A 4776-2025 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>122785011</v>
       </c>
       <c r="B14" t="n">
-        <v>106027</v>
+        <v>106030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 4776-2025 artfynd.xlsx
+++ b/artfynd/A 4776-2025 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>122785011</v>
       </c>
       <c r="B14" t="n">
-        <v>106030</v>
+        <v>106032</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 4776-2025 artfynd.xlsx
+++ b/artfynd/A 4776-2025 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>122785011</v>
       </c>
       <c r="B14" t="n">
-        <v>106032</v>
+        <v>106038</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 4776-2025 artfynd.xlsx
+++ b/artfynd/A 4776-2025 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>122785011</v>
       </c>
       <c r="B14" t="n">
-        <v>106038</v>
+        <v>106041</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 4776-2025 artfynd.xlsx
+++ b/artfynd/A 4776-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16455152</v>
+        <v>16771125</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>1855</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,7 +713,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>327477.4948833782</v>
+        <v>327453</v>
       </c>
       <c r="R2" t="n">
-        <v>6351452.773595403</v>
+        <v>6351526</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,27 +755,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Antalet anger vuxna träd, mindre plantor tillkommer.</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +774,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gammal tomt</t>
+          <t>Åkerkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,55 +796,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94540714</v>
+        <v>16909995</v>
       </c>
       <c r="B3" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>1855</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Varberg, Hl</t>
+          <t>Stavder SV, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327598.0635499619</v>
+        <v>327454</v>
       </c>
       <c r="R3" t="n">
-        <v>6351495.340330532</v>
+        <v>6351527</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,24 +870,19 @@
           <t>Värö</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Arkiv-N-Var-0223</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,68 +897,79 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Lars-Erik Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94539832</v>
+        <v>16455240</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1910</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärglin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Radiola linoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Varberg, Hl</t>
+          <t>Stavder, stranden västerut, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327511.2710430362</v>
+        <v>327005</v>
       </c>
       <c r="R4" t="n">
-        <v>6351469.216606258</v>
+        <v>6352062</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +993,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,81 +1009,88 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Havsstrand, sandig jord mellan block</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ringhals NVI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104317768</v>
+        <v>16455139</v>
       </c>
       <c r="B5" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100084</v>
+        <v>1936</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Kavelhirs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Setaria viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P. Beauv.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogsstigen 5,Varberg, Hl</t>
+          <t>Stavder, sydväst om, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>327343.1389743557</v>
+        <v>327414</v>
       </c>
       <c r="R5" t="n">
-        <v>6351611.071988146</v>
+        <v>6351639</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,22 +1114,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2014-08-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2014-08-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Huvudförekomsten är inprickad.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,31 +1135,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Sandig träda</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Morgan Johansson</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Morgan Johansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ringhals NVI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104321181</v>
+        <v>94539832</v>
       </c>
       <c r="B6" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,16 +1171,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100084</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1198,32 +1188,23 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogsstigen 8,Varberg, Hl</t>
+          <t>Varberg, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>327279.0312725781</v>
+        <v>327511</v>
       </c>
       <c r="R6" t="n">
-        <v>6351685.761440518</v>
+        <v>6351470</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,22 +1228,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,27 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104321187</v>
+        <v>94557474</v>
       </c>
       <c r="B7" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100084</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1322,29 +1288,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogsstigen 8,Varberg 242 m SE, Hl</t>
+          <t>Rösastigen 8, Varberg, Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327455.9035014973</v>
+        <v>327394</v>
       </c>
       <c r="R7" t="n">
-        <v>6351519.720734802</v>
+        <v>6351853</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1371,22 +1328,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,27 +1348,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104321186</v>
+        <v>98709085</v>
       </c>
       <c r="B8" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,27 +1393,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skogsstigen 8,Varberg 41 m NE, Hl</t>
+          <t>Vä 2, Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327316.641648341</v>
+        <v>327125</v>
       </c>
       <c r="R8" t="n">
-        <v>6351703.122949612</v>
+        <v>6352163</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,22 +1445,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hanbo 7 cm. Boplats 1.0 m över marken i krattek. Stort snår vid strandkant som även innehåller en och slån.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,27 +1470,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Boris Berglund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Boris Berglund, Tage Vowles</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104317932</v>
+        <v>104317768</v>
       </c>
       <c r="B9" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>327316.0691148625</v>
+        <v>327343</v>
       </c>
       <c r="R9" t="n">
-        <v>6351612.211302006</v>
+        <v>6351612</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1624,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1634,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,15 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104322487</v>
+        <v>104317771</v>
       </c>
       <c r="B10" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>327335.8821640426</v>
+        <v>327336</v>
       </c>
       <c r="R10" t="n">
-        <v>6351631.946363444</v>
+        <v>6351632</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1744,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1754,12 +1689,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 40cm från marken i solexponerat björnbärssnår</t>
+          <t>I glänta, 60cm från mark i söderläge i björnbörssnår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,15 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104321183</v>
+        <v>104317932</v>
       </c>
       <c r="B11" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,23 +1758,23 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skogsstigen 8,Varberg 42 m NW, Hl</t>
+          <t>Skogsstigen 5,Varberg, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>327249.9877009559</v>
+        <v>327316</v>
       </c>
       <c r="R11" t="n">
-        <v>6351717.295955301</v>
+        <v>6351612</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1873,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1883,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,27 +1828,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Morgan Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Morgan Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104321185</v>
+        <v>104321181</v>
       </c>
       <c r="B12" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,17 +1883,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skogsstigen 8,Varberg 158 m NW, Hl</t>
+          <t>Skogsstigen 8,Varberg, Hl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>327187.4034609403</v>
+        <v>327279</v>
       </c>
       <c r="R12" t="n">
-        <v>6351815.195577055</v>
+        <v>6351686</v>
       </c>
       <c r="S12" t="n">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1997,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2007,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2037,12 +1962,7 @@
         <v>104321182</v>
       </c>
       <c r="B13" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>327210.2942503194</v>
+        <v>327210</v>
       </c>
       <c r="R13" t="n">
-        <v>6351740.618640471</v>
+        <v>6351741</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2158,37 +2078,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122785011</v>
+        <v>104321183</v>
       </c>
       <c r="B14" t="n">
-        <v>106041</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>100084</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2196,19 +2111,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Varberg, Hl</t>
+          <t>Skogsstigen 8,Varberg 42 m NW, Hl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>327473</v>
+        <v>327250</v>
       </c>
       <c r="R14" t="n">
-        <v>6351451</v>
+        <v>6351717</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2232,17 +2155,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ask (EN) 4 stycken och föryngring. Döda skott sy</t>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2257,19 +2185,964 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104321185</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogsstigen 8,Varberg 158 m NW, Hl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>327188</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6351816</v>
+      </c>
+      <c r="S15" t="n">
+        <v>78</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104321186</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skogsstigen 8,Varberg 41 m NE, Hl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>327317</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6351703</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104321187</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skogsstigen 8,Varberg 242 m SE, Hl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>327456</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6351520</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16455208</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stavder, sydväst om, Hl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>327414</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6351639</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2014-08-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2014-08-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Åkerkant, bryn</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Ringhals NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16455152</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stavder, sydväst om, Hl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>327477</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6351453</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2014-08-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2014-08-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Antalet anger vuxna träd, mindre plantor tillkommer.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal tomt</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Ringhals NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122785011</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Varberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>327473</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6351451</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ask (EN) 4 stycken och föryngring. Döda skott sy</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Julius Stölzle</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Magnus Lundström</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16455136</v>
+      </c>
+      <c r="B21" t="n">
+        <v>107295</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221647</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mjukdån</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Galeopsis ladanum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stavder, sydväst om, Hl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>327411</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6351602</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2014-08-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2014-08-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växte egentligen längs med kanterna av hela åkerträdan, men huvudförekomsten är inprickad.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Sandig träda</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Ringhals NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>94540714</v>
+      </c>
+      <c r="B22" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Varberg, Hl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>327598</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6351495</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Värö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
